--- a/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T06:32:12+00:00</t>
+    <t>2026-10-13T12:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
